--- a/TIMA_kullanici_aktarim_sablonu.xlsx
+++ b/TIMA_kullanici_aktarim_sablonu.xlsx
@@ -112,7 +112,7 @@
     <t xml:space="preserve">Rol</t>
   </si>
   <si>
-    <t xml:space="preserve">Talep sahibi: talep açar, kendi taleplerini izler.  Destek personeli: gelen çağrıları karşılar.  Yönetici: ayarları ve kullanıcıları yönetir.</t>
+    <t xml:space="preserve">Talep sahibi: talep açar, kendi taleplerini izler.  Destek personeli: gelen çağrıları karşılar.  Yönetici: ayarları ve kullanıcıları yönetir. TIMA'da Yönetim → Roller'den eklediğin özel rolleri (ör. Saha ekibi) adını aynen yazarak kullanabilirsin.</t>
   </si>
   <si>
     <t xml:space="preserve">Grup</t>
@@ -905,7 +905,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
@@ -8628,7 +8628,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" error="Listeden seçin: Talep sahibi, Destek personeli, Yönetici" errorStyle="stop" errorTitle="Rol" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D501" type="list">
+    <dataValidation allowBlank="true" error="Listede olmayan bir rol yazdın. TIMA'da bu adla bir rol tanımlıysa (ör. Saha ekibi) “Evet” ile devam et." errorStyle="warning" errorTitle="Rol" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D501" type="list">
       <formula1>Listeler!$A$2:$A$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
